--- a/Input/GST_Invoices/Ekm Ser 3/2025/May/Ekm Ser 3_May_2025.xlsx
+++ b/Input/GST_Invoices/Ekm Ser 3/2025/May/Ekm Ser 3_May_2025.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y5"/>
+  <dimension ref="A1:Y8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -952,6 +952,315 @@
         </is>
       </c>
       <c r="Y5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Ekm Ser 3</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> April</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>208299603052025</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> I252082996C00173</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 05-05-2025</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 8c3c4417cc68db643473a80ea20d1a9dd8ecfafde393311df0a2d0865af118e6</t>
+        </is>
+      </c>
+      <c r="I6" s="1" t="n">
+        <v>152521589051008</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 05-05-2025</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> WAR</t>
+        </is>
+      </c>
+      <c r="L6" s="1" t="n">
+        <v>4391</v>
+      </c>
+      <c r="M6" s="1" t="n">
+        <v>2082996</v>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>397.44</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 4,771.67</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 5,169.11</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="n">
+        <v>478.42</v>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>478.42</v>
+      </c>
+      <c r="S6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 6,125.95</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Ekm Ser 3</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> April</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>208299629042025</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> I252082996C00170</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 03-05-2025</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> d7c38d8caa58780062cdabecb8b950337121950cc86ad4521805444462bc2b2b</t>
+        </is>
+      </c>
+      <c r="I7" s="1" t="n">
+        <v>152521568352009</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 03-05-2025</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> WAR</t>
+        </is>
+      </c>
+      <c r="L7" s="1" t="n">
+        <v>4391</v>
+      </c>
+      <c r="M7" s="1" t="n">
+        <v>2082996</v>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 1,000.00</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 1,000.00</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="R7" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="S7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 1,180.00</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Ekm Ser 3</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> April</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>208299630042025</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> I252082996C00171</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 03-05-2025</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 381f06ecbfd273c66ab4713631c3162763d511239167d74c4de0ef7a5a513db4</t>
+        </is>
+      </c>
+      <c r="I8" s="1" t="n">
+        <v>152521568646953</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 03-05-2025</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> WAR</t>
+        </is>
+      </c>
+      <c r="L8" s="1" t="n">
+        <v>4391</v>
+      </c>
+      <c r="M8" s="1" t="n">
+        <v>2082996</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 8,442.61</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 5,924.45</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 14,367.06</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 1,708.50</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 1,708.50</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 17,784.06</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>

--- a/Input/GST_Invoices/Ekm Ser 3/2025/May/Ekm Ser 3_May_2025.xlsx
+++ b/Input/GST_Invoices/Ekm Ser 3/2025/May/Ekm Ser 3_May_2025.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y8"/>
+  <dimension ref="A1:Y15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1261,6 +1261,725 @@
         </is>
       </c>
       <c r="Y8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Ekm Ser 3</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> April</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>208299629042025</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> I252082996C00170</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 03-05-2025</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> d7c38d8caa58780062cdabecb8b950337121950cc86ad4521805444462bc2b2b</t>
+        </is>
+      </c>
+      <c r="I9" s="1" t="n">
+        <v>152521568352009</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 03-05-2025</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> WAR</t>
+        </is>
+      </c>
+      <c r="L9" s="1" t="n">
+        <v>4391</v>
+      </c>
+      <c r="M9" s="1" t="n">
+        <v>2082996</v>
+      </c>
+      <c r="N9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 1,000.00</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 1,000.00</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="R9" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="S9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 1,180.00</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Ekm Ser 3</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> April</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>208299630042025</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> I252082996C00171</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 03-05-2025</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 381f06ecbfd273c66ab4713631c3162763d511239167d74c4de0ef7a5a513db4</t>
+        </is>
+      </c>
+      <c r="I10" s="1" t="n">
+        <v>152521568646953</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 03-05-2025</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> WAR</t>
+        </is>
+      </c>
+      <c r="L10" s="1" t="n">
+        <v>4391</v>
+      </c>
+      <c r="M10" s="1" t="n">
+        <v>2082996</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 8,442.61</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 5,924.45</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 14,367.06</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 1,708.50</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 1,708.50</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 17,784.06</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Ekm Ser 3</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> May</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>208299602052025</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> I252082996C00172</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 03-05-2025</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 762165e905be4b21142355bb41134d9e0c55277970e3bc61e3d9351be51ca6a9</t>
+        </is>
+      </c>
+      <c r="I11" s="1" t="n">
+        <v>152521569659644</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 03-05-2025</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> FSB</t>
+        </is>
+      </c>
+      <c r="L11" s="1" t="n">
+        <v>4391</v>
+      </c>
+      <c r="M11" s="1" t="n">
+        <v>2082996</v>
+      </c>
+      <c r="N11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 7,440.00</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 7,440.00</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="n">
+        <v>669.6</v>
+      </c>
+      <c r="R11" s="2" t="n">
+        <v>669.6</v>
+      </c>
+      <c r="S11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 8,779.20</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Ekm Ser 3</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> May</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>208299602052025</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> I252082996C00172</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 03-05-2025</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 762165e905be4b21142355bb41134d9e0c55277970e3bc61e3d9351be51ca6a9</t>
+        </is>
+      </c>
+      <c r="I12" s="1" t="n">
+        <v>152521569659644</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 03-05-2025</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> FSB</t>
+        </is>
+      </c>
+      <c r="L12" s="1" t="n">
+        <v>4391</v>
+      </c>
+      <c r="M12" s="1" t="n">
+        <v>2082996</v>
+      </c>
+      <c r="N12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 7,440.00</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 7,440.00</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="n">
+        <v>669.6</v>
+      </c>
+      <c r="R12" s="2" t="n">
+        <v>669.6</v>
+      </c>
+      <c r="S12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 8,779.20</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Ekm Ser 3</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> April</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>208299629042025</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> I252082996C00170</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 03-05-2025</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> d7c38d8caa58780062cdabecb8b950337121950cc86ad4521805444462bc2b2b</t>
+        </is>
+      </c>
+      <c r="I13" s="1" t="n">
+        <v>152521568352009</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 03-05-2025</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> WAR</t>
+        </is>
+      </c>
+      <c r="L13" s="1" t="n">
+        <v>4391</v>
+      </c>
+      <c r="M13" s="1" t="n">
+        <v>2082996</v>
+      </c>
+      <c r="N13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 1,000.00</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 1,000.00</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="R13" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="S13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 1,180.00</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Ekm Ser 3</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> April</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>208299630042025</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> I252082996C00171</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 03-05-2025</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 381f06ecbfd273c66ab4713631c3162763d511239167d74c4de0ef7a5a513db4</t>
+        </is>
+      </c>
+      <c r="I14" s="1" t="n">
+        <v>152521568646953</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 03-05-2025</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> WAR</t>
+        </is>
+      </c>
+      <c r="L14" s="1" t="n">
+        <v>4391</v>
+      </c>
+      <c r="M14" s="1" t="n">
+        <v>2082996</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 8,442.61</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 5,924.45</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 14,367.06</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 1,708.50</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 1,708.50</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 17,784.06</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Ekm Ser 3</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> May</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>208299602052025</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> I252082996C00172</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 03-05-2025</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 762165e905be4b21142355bb41134d9e0c55277970e3bc61e3d9351be51ca6a9</t>
+        </is>
+      </c>
+      <c r="I15" s="1" t="n">
+        <v>152521569659644</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 03-05-2025</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> FSB</t>
+        </is>
+      </c>
+      <c r="L15" s="1" t="n">
+        <v>4391</v>
+      </c>
+      <c r="M15" s="1" t="n">
+        <v>2082996</v>
+      </c>
+      <c r="N15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 7,440.00</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 7,440.00</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="n">
+        <v>669.6</v>
+      </c>
+      <c r="R15" s="2" t="n">
+        <v>669.6</v>
+      </c>
+      <c r="S15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 8,779.20</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
